--- a/sectoral_challenges.xlsx
+++ b/sectoral_challenges.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Dr Transition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2B3CE5A-052E-480C-AC28-67BFFE29BC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C75F81-8989-476A-833C-E90140371A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{764F2D09-DADD-4FE0-9E3F-9360E5092BBA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{764F2D09-DADD-4FE0-9E3F-9360E5092BBA}"/>
   </bookViews>
   <sheets>
     <sheet name="Germany" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Italy" sheetId="4" r:id="rId3"/>
     <sheet name="Spain" sheetId="5" r:id="rId4"/>
     <sheet name="Hungry" sheetId="2" r:id="rId5"/>
+    <sheet name="Portugal" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1183,7 +1184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="235">
   <si>
     <t>Policy code</t>
   </si>
@@ -1801,6 +1802,93 @@
   </si>
   <si>
     <t>Ban on the development of new parking lots in city centres</t>
+  </si>
+  <si>
+    <t>PT_EN_AD_1</t>
+  </si>
+  <si>
+    <t>SOLENERGE</t>
+  </si>
+  <si>
+    <t>PT_EN_N_1</t>
+  </si>
+  <si>
+    <t>Accessible Zero-Emission Public Transport for All</t>
+  </si>
+  <si>
+    <t>PT_EN_N_2</t>
+  </si>
+  <si>
+    <t>Agrivoltaics Azores</t>
+  </si>
+  <si>
+    <t>PT_EN_N_3</t>
+  </si>
+  <si>
+    <t>The New Roads</t>
+  </si>
+  <si>
+    <t>PT_HO_N_1</t>
+  </si>
+  <si>
+    <t>Accessible Public Spaces</t>
+  </si>
+  <si>
+    <t>PT_HO_N_2</t>
+  </si>
+  <si>
+    <t>Integrated Neighbourhoods</t>
+  </si>
+  <si>
+    <t>PT_ENHO_N_1</t>
+  </si>
+  <si>
+    <t>Zero VAT on Energy-Efficient Equipment</t>
+  </si>
+  <si>
+    <t>PT_ENHO_N_2</t>
+  </si>
+  <si>
+    <t>Renewable Neighbourhoods</t>
+  </si>
+  <si>
+    <t>Lack of financial stability</t>
+  </si>
+  <si>
+    <t>Tenant decision-making constraints</t>
+  </si>
+  <si>
+    <t>Insufficient public infrastructure &amp; modernisation</t>
+  </si>
+  <si>
+    <t>Absence of policies reflecting real needs</t>
+  </si>
+  <si>
+    <t>Limited accessibility of support</t>
+  </si>
+  <si>
+    <t>Ageing population &amp; low engagement</t>
+  </si>
+  <si>
+    <t>Financial difficulties</t>
+  </si>
+  <si>
+    <t>Restricted access to affordable / social housing</t>
+  </si>
+  <si>
+    <t>Travel &amp; transport burdens linked to housing</t>
+  </si>
+  <si>
+    <t>Lack of home ownership / insecure arrangements</t>
+  </si>
+  <si>
+    <t>Private &amp; family instability</t>
+  </si>
+  <si>
+    <t>Policy mismatch with real needs</t>
+  </si>
+  <si>
+    <t>AI / labour-market risks</t>
   </si>
 </sst>
 </file>
@@ -1919,10 +2007,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1948,9 +2037,28 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{48AFFD0B-92D3-4C35-8CC3-D23ACBDD6C05}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -5643,4 +5751,357 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C047E15E-E0B8-401F-87E5-097BB88FB21C}">
+  <dimension ref="A1:O9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:15" ht="91" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+    </row>
+    <row r="3" spans="1:15" ht="75" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+    </row>
+    <row r="4" spans="1:15" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+    </row>
+    <row r="5" spans="1:15" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+    </row>
+    <row r="6" spans="1:15" ht="37.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="50" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="75" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="L8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="50" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9" s="14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>